--- a/templates/samples/SALES_EBAY_SAMPLE.xlsx
+++ b/templates/samples/SALES_EBAY_SAMPLE.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:S21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -519,31 +519,31 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-08</v>
       </c>
       <c r="B3" t="str">
-        <v>EBA-5006</v>
+        <v>EBA-5007</v>
       </c>
       <c r="C3" t="str">
-        <v>SAM-256GB-WHI</v>
+        <v>GOO-128GB-WHI</v>
       </c>
       <c r="D3" t="str">
-        <v>350100000047514</v>
+        <v>350100000055433</v>
       </c>
       <c r="E3" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>CELLHUB TRADING</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>446.53</v>
+        <v>260.29</v>
       </c>
       <c r="H3">
-        <v>643.55</v>
+        <v>371.44</v>
       </c>
       <c r="I3">
-        <v>197.01999999999998</v>
+        <v>111.14999999999998</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -578,31 +578,31 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-07-11</v>
+        <v>2026-07-13</v>
       </c>
       <c r="B4" t="str">
-        <v>EBA-5010</v>
+        <v>EBA-5012</v>
       </c>
       <c r="C4" t="str">
-        <v>IPH-128GB-GRE</v>
+        <v>SAM-128GB-BLU</v>
       </c>
       <c r="D4" t="str">
-        <v>350100000079190</v>
+        <v>350100000102947</v>
       </c>
       <c r="E4" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>311.8</v>
+        <v>230.57</v>
       </c>
       <c r="H4">
-        <v>466.51</v>
+        <v>319.34</v>
       </c>
       <c r="I4">
-        <v>154.70999999999998</v>
+        <v>88.76999999999998</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -623,7 +623,7 @@
         <v/>
       </c>
       <c r="P4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q4" t="str">
         <v/>
@@ -637,31 +637,31 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-07-15</v>
+        <v>2026-07-18</v>
       </c>
       <c r="B5" t="str">
-        <v>EBA-5014</v>
+        <v>EBA-5017</v>
       </c>
       <c r="C5" t="str">
-        <v>SAM-256GB-WHI</v>
+        <v>IPH-128GB-GRA</v>
       </c>
       <c r="D5" t="str">
-        <v>350100000110866</v>
+        <v>350100000134623</v>
       </c>
       <c r="E5" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>CELLHUB TRADING</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>450.57</v>
+        <v>219.35</v>
       </c>
       <c r="H5">
-        <v>611.06</v>
+        <v>322.18</v>
       </c>
       <c r="I5">
-        <v>160.48999999999995</v>
+        <v>102.83000000000001</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -682,7 +682,7 @@
         <v/>
       </c>
       <c r="P5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="str">
         <v/>
@@ -696,16 +696,16 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-07-19</v>
+        <v>2026-07-23</v>
       </c>
       <c r="B6" t="str">
-        <v>EBA-5018</v>
+        <v>EBA-5022</v>
       </c>
       <c r="C6" t="str">
-        <v>IPH-128GB-BLU</v>
+        <v>SAM-256GB-MID</v>
       </c>
       <c r="D6" t="str">
-        <v>350100000142542</v>
+        <v>350100000174218</v>
       </c>
       <c r="E6" t="str">
         <v>CELLHUB TRADING</v>
@@ -714,13 +714,13 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>316.37</v>
+        <v>449.53</v>
       </c>
       <c r="H6">
-        <v>464.68</v>
+        <v>632.67</v>
       </c>
       <c r="I6">
-        <v>148.31</v>
+        <v>183.14</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -741,7 +741,7 @@
         <v/>
       </c>
       <c r="P6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q6" t="str">
         <v/>
@@ -755,31 +755,31 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-07-23</v>
+        <v>2026-07-04</v>
       </c>
       <c r="B7" t="str">
-        <v>EBA-5022</v>
+        <v>EBA-5027</v>
       </c>
       <c r="C7" t="str">
-        <v>SAM-256GB-MID</v>
+        <v>IPH-256GB-MID</v>
       </c>
       <c r="D7" t="str">
-        <v>350100000174218</v>
+        <v>350100000213813</v>
       </c>
       <c r="E7" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7">
-        <v>449.53</v>
+        <v>499.91</v>
       </c>
       <c r="H7">
-        <v>590.13</v>
+        <v>726.64</v>
       </c>
       <c r="I7">
-        <v>140.60000000000002</v>
+        <v>226.72999999999996</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -814,16 +814,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-07-03</v>
+        <v>2026-07-09</v>
       </c>
       <c r="B8" t="str">
-        <v>EBA-5026</v>
+        <v>EBA-5032</v>
       </c>
       <c r="C8" t="str">
-        <v>IPH-128GB-PUR</v>
+        <v>IPH-64GB-GRE</v>
       </c>
       <c r="D8" t="str">
-        <v>350100000205894</v>
+        <v>350100000253408</v>
       </c>
       <c r="E8" t="str">
         <v>PHONEBOX DIRECT</v>
@@ -832,13 +832,13 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>325.88</v>
+        <v>196.32</v>
       </c>
       <c r="H8">
-        <v>461.56</v>
+        <v>281.67</v>
       </c>
       <c r="I8">
-        <v>135.68</v>
+        <v>85.35000000000002</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -873,16 +873,16 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-14</v>
       </c>
       <c r="B9" t="str">
-        <v>EBA-5030</v>
+        <v>EBA-5037</v>
       </c>
       <c r="C9" t="str">
-        <v>SAM-256GB-GRA</v>
+        <v>SAM-128GB-GRE</v>
       </c>
       <c r="D9" t="str">
-        <v>350100000237570</v>
+        <v>350100000293003</v>
       </c>
       <c r="E9" t="str">
         <v>MOBILE WHOLESALE LTD</v>
@@ -891,13 +891,13 @@
         <v>1</v>
       </c>
       <c r="G9">
-        <v>418.34</v>
+        <v>262.94</v>
       </c>
       <c r="H9">
-        <v>567.87</v>
+        <v>393.16</v>
       </c>
       <c r="I9">
-        <v>149.53000000000003</v>
+        <v>130.22000000000003</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -932,31 +932,31 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-07-11</v>
+        <v>2026-07-19</v>
       </c>
       <c r="B10" t="str">
-        <v>EBA-5034</v>
+        <v>EBA-5042</v>
       </c>
       <c r="C10" t="str">
-        <v>IPH-128GB-GRE</v>
+        <v>IPH-128GB-WHI</v>
       </c>
       <c r="D10" t="str">
-        <v>350100000269246</v>
+        <v>350100000332598</v>
       </c>
       <c r="E10" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>NORTHSIDE STOCK</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10">
-        <v>305.4</v>
+        <v>334.64</v>
       </c>
       <c r="H10">
-        <v>438.18</v>
+        <v>432.05</v>
       </c>
       <c r="I10">
-        <v>132.78000000000003</v>
+        <v>97.41000000000003</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v/>
       </c>
       <c r="P10">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="str">
         <v/>
@@ -991,31 +991,31 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-07-15</v>
+        <v>2026-07-24</v>
       </c>
       <c r="B11" t="str">
-        <v>EBA-5038</v>
+        <v>EBA-5047</v>
       </c>
       <c r="C11" t="str">
-        <v>SAM-256GB-MID</v>
+        <v>GOO-128GB-GRA</v>
       </c>
       <c r="D11" t="str">
-        <v>350100000300922</v>
+        <v>350100000372193</v>
       </c>
       <c r="E11" t="str">
-        <v>NORTHSIDE STOCK</v>
+        <v>CELLHUB TRADING</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11">
-        <v>422.16</v>
+        <v>256.93</v>
       </c>
       <c r="H11">
-        <v>623.08</v>
+        <v>344.13</v>
       </c>
       <c r="I11">
-        <v>200.92000000000002</v>
+        <v>87.19999999999999</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -1050,31 +1050,31 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-07-19</v>
+        <v>2026-07-05</v>
       </c>
       <c r="B12" t="str">
-        <v>EBA-5042</v>
+        <v>EBA-5052</v>
       </c>
       <c r="C12" t="str">
-        <v>IPH-128GB-WHI</v>
+        <v>IPH-256GB-PUR</v>
       </c>
       <c r="D12" t="str">
-        <v>350100000332598</v>
+        <v>350100000411788</v>
       </c>
       <c r="E12" t="str">
-        <v>NORTHSIDE STOCK</v>
+        <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12">
-        <v>334.64</v>
+        <v>497.17</v>
       </c>
       <c r="H12">
-        <v>424.77</v>
+        <v>654.36</v>
       </c>
       <c r="I12">
-        <v>90.13</v>
+        <v>157.19</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -1095,7 +1095,7 @@
         <v/>
       </c>
       <c r="P12">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q12" t="str">
         <v/>
@@ -1109,31 +1109,31 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-07-23</v>
+        <v>2026-07-10</v>
       </c>
       <c r="B13" t="str">
-        <v>EBA-5046</v>
+        <v>EBA-5057</v>
       </c>
       <c r="C13" t="str">
-        <v>SAM-256GB-PUR</v>
+        <v>IPH-128GB-BLA</v>
       </c>
       <c r="D13" t="str">
-        <v>350100000364274</v>
+        <v>350100000451383</v>
       </c>
       <c r="E13" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13">
-        <v>453.75</v>
+        <v>218.51</v>
       </c>
       <c r="H13">
-        <v>660.67</v>
+        <v>303.91</v>
       </c>
       <c r="I13">
-        <v>206.91999999999996</v>
+        <v>85.40000000000003</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -1154,7 +1154,7 @@
         <v/>
       </c>
       <c r="P13">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q13" t="str">
         <v/>
@@ -1168,31 +1168,31 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-07-03</v>
+        <v>2026-07-15</v>
       </c>
       <c r="B14" t="str">
-        <v>EBA-5050</v>
+        <v>EBA-5062</v>
       </c>
       <c r="C14" t="str">
-        <v>IPH-128GB-BLU</v>
+        <v>SAM-256GB-BLU</v>
       </c>
       <c r="D14" t="str">
-        <v>350100000395950</v>
+        <v>350100000490978</v>
       </c>
       <c r="E14" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>CELLHUB TRADING</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14">
-        <v>316.67</v>
+        <v>431.55</v>
       </c>
       <c r="H14">
-        <v>424.14</v>
+        <v>555.17</v>
       </c>
       <c r="I14">
-        <v>107.46999999999997</v>
+        <v>123.61999999999995</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -1227,31 +1227,31 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-20</v>
       </c>
       <c r="B15" t="str">
-        <v>EBA-5054</v>
+        <v>EBA-5067</v>
       </c>
       <c r="C15" t="str">
-        <v>SAM-256GB-GRA</v>
+        <v>IPH-256GB-GRA</v>
       </c>
       <c r="D15" t="str">
-        <v>350100000427626</v>
+        <v>350100000530573</v>
       </c>
       <c r="E15" t="str">
-        <v>NORTHSIDE STOCK</v>
+        <v>CELLHUB TRADING</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15">
-        <v>405.86</v>
+        <v>500.16</v>
       </c>
       <c r="H15">
-        <v>602.26</v>
+        <v>745.1</v>
       </c>
       <c r="I15">
-        <v>196.39999999999998</v>
+        <v>244.94</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -1286,31 +1286,31 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-07-11</v>
+        <v>2026-07-01</v>
       </c>
       <c r="B16" t="str">
-        <v>EBA-5058</v>
+        <v>EBA-5072</v>
       </c>
       <c r="C16" t="str">
-        <v>IPH-128GB-WHI</v>
+        <v>IPH-128GB-MID</v>
       </c>
       <c r="D16" t="str">
-        <v>350100000459302</v>
+        <v>350100000578087</v>
       </c>
       <c r="E16" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>NORTHSIDE STOCK</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16">
-        <v>336.42</v>
+        <v>222.91</v>
       </c>
       <c r="H16">
-        <v>447.02</v>
+        <v>314.64</v>
       </c>
       <c r="I16">
-        <v>110.59999999999997</v>
+        <v>91.72999999999999</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1345,31 +1345,31 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-07-15</v>
+        <v>2026-07-06</v>
       </c>
       <c r="B17" t="str">
-        <v>EBA-5062</v>
+        <v>EBA-5077</v>
       </c>
       <c r="C17" t="str">
-        <v>SAM-256GB-BLU</v>
+        <v>SAM-128GB-WHI</v>
       </c>
       <c r="D17" t="str">
-        <v>350100000490978</v>
+        <v>350100000609763</v>
       </c>
       <c r="E17" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17">
-        <v>431.55</v>
+        <v>257.31</v>
       </c>
       <c r="H17">
-        <v>553.53</v>
+        <v>378.96</v>
       </c>
       <c r="I17">
-        <v>121.97999999999996</v>
+        <v>121.64999999999998</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1404,31 +1404,31 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-07-19</v>
+        <v>2026-07-11</v>
       </c>
       <c r="B18" t="str">
-        <v>EBA-5066</v>
+        <v>EBA-5082</v>
       </c>
       <c r="C18" t="str">
-        <v>IPH-128GB-BLA</v>
+        <v>IPH-128GB-MID</v>
       </c>
       <c r="D18" t="str">
-        <v>350100000522654</v>
+        <v>350100000649358</v>
       </c>
       <c r="E18" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18">
-        <v>337.53</v>
+        <v>315.22</v>
       </c>
       <c r="H18">
-        <v>434.22</v>
+        <v>397.26</v>
       </c>
       <c r="I18">
-        <v>96.69000000000005</v>
+        <v>82.03999999999996</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -1463,31 +1463,31 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-07-23</v>
+        <v>2026-07-16</v>
       </c>
       <c r="B19" t="str">
-        <v>EBA-5070</v>
+        <v>EBA-5087</v>
       </c>
       <c r="C19" t="str">
-        <v>SAM-256GB-GRA</v>
+        <v>GOO-128GB-STA</v>
       </c>
       <c r="D19" t="str">
-        <v>350100000554330</v>
+        <v>350100000688953</v>
       </c>
       <c r="E19" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19">
-        <v>451.39</v>
+        <v>275.49</v>
       </c>
       <c r="H19">
-        <v>605.91</v>
+        <v>405.63</v>
       </c>
       <c r="I19">
-        <v>154.51999999999998</v>
+        <v>130.14</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -1508,7 +1508,7 @@
         <v/>
       </c>
       <c r="P19">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q19" t="str">
         <v/>
@@ -1522,31 +1522,31 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-07-03</v>
+        <v>2026-07-21</v>
       </c>
       <c r="B20" t="str">
-        <v>EBA-5074</v>
+        <v>EBA-5092</v>
       </c>
       <c r="C20" t="str">
-        <v>IPH-128GB-PUR</v>
+        <v>IPH-256GB-GRA</v>
       </c>
       <c r="D20" t="str">
-        <v>350100000586006</v>
+        <v>350100007855648</v>
       </c>
       <c r="E20" t="str">
-        <v>NORTHSIDE STOCK</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20">
-        <v>334.66</v>
+        <v>462.92</v>
       </c>
       <c r="H20">
-        <v>451.26</v>
+        <v>686.89</v>
       </c>
       <c r="I20">
-        <v>116.59999999999997</v>
+        <v>223.96999999999997</v>
       </c>
       <c r="J20" t="str">
         <v/>
@@ -1581,16 +1581,16 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-02</v>
       </c>
       <c r="B21" t="str">
-        <v>EBA-5078</v>
+        <v>EBA-5097</v>
       </c>
       <c r="C21" t="str">
-        <v>SAM-256GB-GRE</v>
+        <v>IPH-128GB-GRA</v>
       </c>
       <c r="D21" t="str">
-        <v>350100000617682</v>
+        <v>350100007895243</v>
       </c>
       <c r="E21" t="str">
         <v>PHONEBOX DIRECT</v>
@@ -1599,13 +1599,13 @@
         <v>1</v>
       </c>
       <c r="G21">
-        <v>422.7</v>
+        <v>223.04</v>
       </c>
       <c r="H21">
-        <v>579.8</v>
+        <v>305.42</v>
       </c>
       <c r="I21">
-        <v>157.09999999999997</v>
+        <v>82.38000000000002</v>
       </c>
       <c r="J21" t="str">
         <v/>
@@ -1626,7 +1626,7 @@
         <v/>
       </c>
       <c r="P21">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="str">
         <v/>
@@ -1635,307 +1635,12 @@
         <v/>
       </c>
       <c r="S21" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>2026-07-11</v>
-      </c>
-      <c r="B22" t="str">
-        <v>EBA-5082</v>
-      </c>
-      <c r="C22" t="str">
-        <v>IPH-128GB-MID</v>
-      </c>
-      <c r="D22" t="str">
-        <v>350100000649358</v>
-      </c>
-      <c r="E22" t="str">
-        <v>PHONEBOX DIRECT</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22">
-        <v>315.22</v>
-      </c>
-      <c r="H22">
-        <v>464.25</v>
-      </c>
-      <c r="I22">
-        <v>149.02999999999997</v>
-      </c>
-      <c r="J22" t="str">
-        <v/>
-      </c>
-      <c r="K22" t="str">
-        <v/>
-      </c>
-      <c r="L22" t="str">
-        <v/>
-      </c>
-      <c r="M22" t="str">
-        <v/>
-      </c>
-      <c r="N22" t="str">
-        <v/>
-      </c>
-      <c r="O22" t="str">
-        <v/>
-      </c>
-      <c r="P22">
-        <v>8</v>
-      </c>
-      <c r="Q22" t="str">
-        <v/>
-      </c>
-      <c r="R22" t="str">
-        <v/>
-      </c>
-      <c r="S22" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>2026-07-15</v>
-      </c>
-      <c r="B23" t="str">
-        <v>EBA-5086</v>
-      </c>
-      <c r="C23" t="str">
-        <v>SAM-256GB-GRA</v>
-      </c>
-      <c r="D23" t="str">
-        <v>350100000681034</v>
-      </c>
-      <c r="E23" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23">
-        <v>413.46</v>
-      </c>
-      <c r="H23">
-        <v>568.64</v>
-      </c>
-      <c r="I23">
-        <v>155.18</v>
-      </c>
-      <c r="J23" t="str">
-        <v/>
-      </c>
-      <c r="K23" t="str">
-        <v/>
-      </c>
-      <c r="L23" t="str">
-        <v/>
-      </c>
-      <c r="M23" t="str">
-        <v/>
-      </c>
-      <c r="N23" t="str">
-        <v/>
-      </c>
-      <c r="O23" t="str">
-        <v/>
-      </c>
-      <c r="P23">
-        <v>8</v>
-      </c>
-      <c r="Q23" t="str">
-        <v/>
-      </c>
-      <c r="R23" t="str">
-        <v/>
-      </c>
-      <c r="S23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>2026-07-19</v>
-      </c>
-      <c r="B24" t="str">
-        <v>EBA-5090</v>
-      </c>
-      <c r="C24" t="str">
-        <v>IPH-128GB-GRA</v>
-      </c>
-      <c r="D24" t="str">
-        <v>350100007839810</v>
-      </c>
-      <c r="E24" t="str">
-        <v>PHONEBOX DIRECT</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24">
-        <v>335.04</v>
-      </c>
-      <c r="H24">
-        <v>490.45</v>
-      </c>
-      <c r="I24">
-        <v>155.40999999999997</v>
-      </c>
-      <c r="J24" t="str">
-        <v/>
-      </c>
-      <c r="K24" t="str">
-        <v/>
-      </c>
-      <c r="L24" t="str">
-        <v/>
-      </c>
-      <c r="M24" t="str">
-        <v/>
-      </c>
-      <c r="N24" t="str">
-        <v/>
-      </c>
-      <c r="O24" t="str">
-        <v/>
-      </c>
-      <c r="P24">
-        <v>8</v>
-      </c>
-      <c r="Q24" t="str">
-        <v/>
-      </c>
-      <c r="R24" t="str">
-        <v/>
-      </c>
-      <c r="S24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>2026-07-23</v>
-      </c>
-      <c r="B25" t="str">
-        <v>EBA-5094</v>
-      </c>
-      <c r="C25" t="str">
-        <v>SAM-256GB-PUR</v>
-      </c>
-      <c r="D25" t="str">
-        <v>350100007871486</v>
-      </c>
-      <c r="E25" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25">
-        <v>417.16</v>
-      </c>
-      <c r="H25">
-        <v>583.93</v>
-      </c>
-      <c r="I25">
-        <v>166.76999999999992</v>
-      </c>
-      <c r="J25" t="str">
-        <v/>
-      </c>
-      <c r="K25" t="str">
-        <v/>
-      </c>
-      <c r="L25" t="str">
-        <v/>
-      </c>
-      <c r="M25" t="str">
-        <v/>
-      </c>
-      <c r="N25" t="str">
-        <v/>
-      </c>
-      <c r="O25" t="str">
-        <v/>
-      </c>
-      <c r="P25">
-        <v>8</v>
-      </c>
-      <c r="Q25" t="str">
-        <v/>
-      </c>
-      <c r="R25" t="str">
-        <v/>
-      </c>
-      <c r="S25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>2026-07-03</v>
-      </c>
-      <c r="B26" t="str">
-        <v>EBA-5098</v>
-      </c>
-      <c r="C26" t="str">
-        <v>IPH-128GB-BLA</v>
-      </c>
-      <c r="D26" t="str">
-        <v>350100007903162</v>
-      </c>
-      <c r="E26" t="str">
-        <v>CELLHUB TRADING</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26">
-        <v>327.58</v>
-      </c>
-      <c r="H26">
-        <v>486.07</v>
-      </c>
-      <c r="I26">
-        <v>158.49</v>
-      </c>
-      <c r="J26" t="str">
-        <v/>
-      </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
-      <c r="L26" t="str">
-        <v/>
-      </c>
-      <c r="M26" t="str">
-        <v/>
-      </c>
-      <c r="N26" t="str">
-        <v/>
-      </c>
-      <c r="O26" t="str">
-        <v/>
-      </c>
-      <c r="P26">
-        <v>8</v>
-      </c>
-      <c r="Q26" t="str">
-        <v/>
-      </c>
-      <c r="R26" t="str">
-        <v/>
-      </c>
-      <c r="S26" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S21"/>
   </ignoredErrors>
 </worksheet>
 </file>